--- a/scripts/example_input/dummy_traject/16-X_004_DP015-DP018.xlsx
+++ b/scripts/example_input/dummy_traject/16-X_004_DP015-DP018.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAKA\sources\github\faalkansbeheer\scripts\example_input\dummy_traject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D302231-DA68-4A05-953D-A8D1DD37F4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFDCFD3-FA9D-4A70-8B59-9740B2DFF5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,9 +185,6 @@
     <t>16-X</t>
   </si>
   <si>
-    <t>groene dijk</t>
-  </si>
-  <si>
     <t>016-01_0145_9_BO_km0954</t>
   </si>
   <si>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>fc curve</t>
+  </si>
+  <si>
+    <t>Testcase 3</t>
   </si>
 </sst>
 </file>
@@ -1097,14 +1097,14 @@
         <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="5">
         <f>C6-B6</f>
         <v>300</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>40</v>
@@ -1119,10 +1119,10 @@
         <v>1600</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N6" s="24">
         <v>7</v>
@@ -1207,7 +1207,7 @@
         <v>29</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -1975,6 +1975,50 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-39893</_dlc_DocId>
+    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
+        </TermInfo>
+      </Terms>
+    </e39ed97c196f40ca8994d73dd80b64d0>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Value>2</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
+        </TermInfo>
+      </Terms>
+    </n3c4235fe90e4626a88beeb52e343114>
+    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-39893</Url>
+      <Description>CBPJ-627581585-39893</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -2022,50 +2066,6 @@
     <Filter/>
   </Receiver>
 </spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-39893</_dlc_DocId>
-    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
-        </TermInfo>
-      </Terms>
-    </e39ed97c196f40ca8994d73dd80b64d0>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Value>2</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
-        </TermInfo>
-      </Terms>
-    </n3c4235fe90e4626a88beeb52e343114>
-    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-39893</Url>
-      <Description>CBPJ-627581585-39893</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2351,9 +2351,12 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB6BAA4-1CD2-494A-9433-1FC41C42B0F8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633EBDFC-B21A-4048-98F2-0CE0F24CB488}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
+    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2367,12 +2370,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633EBDFC-B21A-4048-98F2-0CE0F24CB488}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB6BAA4-1CD2-494A-9433-1FC41C42B0F8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
-    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
